--- a/artfynd/A 53423-2024 artfynd.xlsx
+++ b/artfynd/A 53423-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114729885</v>
+        <v>114729883</v>
       </c>
       <c r="B2" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>214</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörkhövdad spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Allocalicium adaequatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749767</v>
+        <v>749943</v>
       </c>
       <c r="R2" t="n">
-        <v>7217079</v>
+        <v>7217073</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,55 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114729888</v>
+        <v>114729889</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749780</v>
+        <v>749850</v>
       </c>
       <c r="R3" t="n">
-        <v>7217119</v>
+        <v>7217123</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114729886</v>
+        <v>114729885</v>
       </c>
       <c r="B4" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749766</v>
+        <v>749767</v>
       </c>
       <c r="R4" t="n">
-        <v>7217108</v>
+        <v>7217079</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114729889</v>
+        <v>114729886</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749850</v>
+        <v>749766</v>
       </c>
       <c r="R5" t="n">
-        <v>7217123</v>
+        <v>7217108</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,12 +1106,7 @@
         <v>114729887</v>
       </c>
       <c r="B6" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,50 +1210,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119537216</v>
+        <v>114729888</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storbäcken, Vb</t>
+          <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750046</v>
+        <v>749780</v>
       </c>
       <c r="R7" t="n">
-        <v>7216935</v>
+        <v>7217119</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,22 +1280,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,6 +1319,113 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119537216</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>750046</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7216935</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53423-2024 artfynd.xlsx
+++ b/artfynd/A 53423-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114729883</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119537216</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114729889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114729885</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114729886</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114729887</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,8 +1461,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114729888</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>